--- a/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.034</v>
+        <v>0.0306</v>
       </c>
       <c r="E2">
-        <v>-0.0142</v>
+        <v>0.00437</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1087.3</v>
+        <v>968.36</v>
       </c>
       <c r="L2">
-        <v>0.1835663155051324</v>
+        <v>0.1939318687040635</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6118.4</v>
+        <v>5653.5</v>
       </c>
       <c r="V2">
-        <v>0.2525175818007726</v>
+        <v>0.3356507593478752</v>
       </c>
       <c r="W2">
-        <v>0.08512659948874207</v>
+        <v>0.07480713784773631</v>
       </c>
       <c r="X2">
-        <v>0.08503492034546029</v>
+        <v>0.1617524565449917</v>
       </c>
       <c r="Y2">
-        <v>9.16791432817865e-05</v>
+        <v>-0.08694531869725534</v>
       </c>
       <c r="Z2">
-        <v>0.2048090288583224</v>
+        <v>0.1688595445563907</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05607295871824241</v>
+        <v>0.08488788474105519</v>
       </c>
       <c r="AC2">
-        <v>-0.05607295871824241</v>
+        <v>-0.08488788474105519</v>
       </c>
       <c r="AD2">
-        <v>24562.5</v>
+        <v>25437.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24562.5</v>
+        <v>25437.5</v>
       </c>
       <c r="AG2">
-        <v>18444.1</v>
+        <v>19784</v>
       </c>
       <c r="AH2">
-        <v>0.5034114129131561</v>
+        <v>0.6016309965019667</v>
       </c>
       <c r="AI2">
-        <v>0.5933458303338922</v>
+        <v>0.6417598663878034</v>
       </c>
       <c r="AJ2">
-        <v>0.4322123462460485</v>
+        <v>0.5401420794268772</v>
       </c>
       <c r="AK2">
-        <v>0.5228186245329978</v>
+        <v>0.5821631610541556</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crédit du Maroc S.A. (CBSE:CDM)</t>
+          <t>Bank of Africa (CBSE:BOA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0635</v>
+        <v>0.00234</v>
       </c>
       <c r="E3">
-        <v>0.172</v>
+        <v>0.00437</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>52.6</v>
+        <v>192</v>
       </c>
       <c r="L3">
-        <v>0.2256542256542257</v>
+        <v>0.1744502998364529</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>164</v>
+        <v>1579.8</v>
       </c>
       <c r="V3">
-        <v>0.2323604420515727</v>
+        <v>0.4596584131048328</v>
       </c>
       <c r="W3">
-        <v>0.08942536552193131</v>
+        <v>0.07480713784773631</v>
       </c>
       <c r="X3">
-        <v>0.07532865844470531</v>
+        <v>0.1617524565449917</v>
       </c>
       <c r="Y3">
-        <v>0.014096707077226</v>
+        <v>-0.08694531869725534</v>
       </c>
       <c r="Z3">
-        <v>0.2119861767915605</v>
+        <v>0.1009817414441692</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05508249677654078</v>
+        <v>0.08481751050623643</v>
       </c>
       <c r="AC3">
-        <v>-0.05508249677654078</v>
+        <v>-0.08481751050623643</v>
       </c>
       <c r="AD3">
-        <v>588</v>
+        <v>8517.200000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>588</v>
+        <v>8517.200000000001</v>
       </c>
       <c r="AG3">
-        <v>424</v>
+        <v>6937.400000000001</v>
       </c>
       <c r="AH3">
-        <v>0.4544751893646622</v>
+        <v>0.7124919483691788</v>
       </c>
       <c r="AI3">
-        <v>0.4680038204393505</v>
+        <v>0.7518382839740478</v>
       </c>
       <c r="AJ3">
-        <v>0.3752876615330147</v>
+        <v>0.6687101780361084</v>
       </c>
       <c r="AK3">
-        <v>0.3881362138410838</v>
+        <v>0.7116230882066327</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
+          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00565</v>
+        <v>0.103</v>
       </c>
       <c r="E4">
-        <v>-0.114</v>
+        <v>0.159</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>29.2</v>
+        <v>70.5</v>
       </c>
       <c r="L4">
-        <v>0.1106479727169382</v>
+        <v>0.2534148094895758</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,55 +871,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>171.7</v>
+        <v>262.2</v>
       </c>
       <c r="V4">
-        <v>0.1848422865755194</v>
+        <v>0.2952702702702703</v>
       </c>
       <c r="W4">
-        <v>0.03554906257608961</v>
+        <v>0.1249335459861776</v>
       </c>
       <c r="X4">
-        <v>0.09474118224621528</v>
+        <v>0.1948067725151487</v>
       </c>
       <c r="Y4">
-        <v>-0.05919211967012567</v>
+        <v>-0.06987322652897114</v>
       </c>
       <c r="Z4">
-        <v>0.1337014895126153</v>
+        <v>0.09208566416206018</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05567998634490823</v>
+        <v>0.08487825960676895</v>
       </c>
       <c r="AC4">
-        <v>-0.05567998634490823</v>
+        <v>-0.08487825960676895</v>
       </c>
       <c r="AD4">
-        <v>1457.2</v>
+        <v>3138.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1457.2</v>
+        <v>3138.2</v>
       </c>
       <c r="AG4">
-        <v>1285.5</v>
+        <v>2876</v>
       </c>
       <c r="AH4">
-        <v>0.6107036586899125</v>
+        <v>0.7794446376235656</v>
       </c>
       <c r="AI4">
-        <v>0.6450070821529745</v>
+        <v>0.8447375504710632</v>
       </c>
       <c r="AJ4">
-        <v>0.5805184248554913</v>
+        <v>0.7640807651434643</v>
       </c>
       <c r="AK4">
-        <v>0.6158083832335329</v>
+        <v>0.832947173308619</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank of Africa (CBSE:BOA)</t>
+          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0211</v>
+        <v>-0.0025</v>
       </c>
       <c r="E5">
-        <v>-0.022</v>
+        <v>-0.276</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>198.4</v>
+        <v>9.66</v>
       </c>
       <c r="L5">
-        <v>0.1511734227369704</v>
+        <v>0.04216499345264077</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -990,55 +990,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1510.6</v>
+        <v>113.9</v>
       </c>
       <c r="V5">
-        <v>0.3614740368509213</v>
+        <v>0.252886323268206</v>
       </c>
       <c r="W5">
-        <v>0.08082783345555285</v>
+        <v>0.01208104052026013</v>
       </c>
       <c r="X5">
-        <v>0.1162173574136309</v>
+        <v>0.2019786817067487</v>
       </c>
       <c r="Y5">
-        <v>-0.03538952395807803</v>
+        <v>-0.1898976411864886</v>
       </c>
       <c r="Z5">
-        <v>0.1300526195832054</v>
+        <v>0.1103867632249702</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05603820049365998</v>
+        <v>0.08488788474105519</v>
       </c>
       <c r="AC5">
-        <v>-0.05603820049365998</v>
+        <v>-0.08488788474105519</v>
       </c>
       <c r="AD5">
-        <v>9956.799999999999</v>
+        <v>1694.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9956.799999999999</v>
+        <v>1694.9</v>
       </c>
       <c r="AG5">
-        <v>8446.199999999999</v>
+        <v>1581</v>
       </c>
       <c r="AH5">
-        <v>0.7043676339506784</v>
+        <v>0.7900526732857875</v>
       </c>
       <c r="AI5">
-        <v>0.7578165433677353</v>
+        <v>0.7204675876726887</v>
       </c>
       <c r="AJ5">
-        <v>0.6689953426480373</v>
+        <v>0.7782809884808506</v>
       </c>
       <c r="AK5">
-        <v>0.7263548958566244</v>
+        <v>0.7062449745376574</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
+          <t>Banque Centrale Populaire (CBSE:BCP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0776</v>
+        <v>0.0368</v>
       </c>
       <c r="E6">
-        <v>-0.0064</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>49.7</v>
+        <v>163</v>
       </c>
       <c r="L6">
-        <v>0.181784930504755</v>
+        <v>0.1208033795301267</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1109,55 +1109,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>213.6</v>
+        <v>1616.5</v>
       </c>
       <c r="V6">
-        <v>0.2057605240342934</v>
+        <v>0.3598299350013356</v>
       </c>
       <c r="W6">
-        <v>0.08993847267462902</v>
+        <v>0.04461597416105546</v>
       </c>
       <c r="X6">
-        <v>0.1220651056045114</v>
+        <v>0.1130275653939952</v>
       </c>
       <c r="Y6">
-        <v>-0.03212663292988235</v>
+        <v>-0.06841159123293974</v>
       </c>
       <c r="Z6">
-        <v>0.08727017364657813</v>
+        <v>0.202127181484533</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05610771694282483</v>
+        <v>0.09215197647189804</v>
       </c>
       <c r="AC6">
-        <v>-0.05610771694282483</v>
+        <v>-0.09215197647189804</v>
       </c>
       <c r="AD6">
-        <v>2703.4</v>
+        <v>4140.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2703.4</v>
+        <v>4140.9</v>
       </c>
       <c r="AG6">
-        <v>2489.8</v>
+        <v>2524.4</v>
       </c>
       <c r="AH6">
-        <v>0.7225444340505145</v>
+        <v>0.4796427785435465</v>
       </c>
       <c r="AI6">
-        <v>0.8131504541899777</v>
+        <v>0.4744548964790264</v>
       </c>
       <c r="AJ6">
-        <v>0.7057456277105361</v>
+        <v>0.3597651351043211</v>
       </c>
       <c r="AK6">
-        <v>0.8003214400514305</v>
+        <v>0.354989312633592</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.035</v>
+        <v>0.0306</v>
       </c>
       <c r="E7">
-        <v>0.0104</v>
+        <v>0.0191</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>536.8</v>
+        <v>533.2</v>
       </c>
       <c r="L7">
-        <v>0.2394931739091639</v>
+        <v>0.2618731889396396</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1228,179 +1228,60 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2226.2</v>
+        <v>2081.1</v>
       </c>
       <c r="V7">
-        <v>0.2094084226170879</v>
+        <v>0.2747072877753871</v>
       </c>
       <c r="W7">
-        <v>0.1002614867388868</v>
+        <v>0.09454738895292136</v>
       </c>
       <c r="X7">
-        <v>0.0651132480109063</v>
+        <v>0.1170085266950098</v>
       </c>
       <c r="Y7">
-        <v>0.03514823872798051</v>
+        <v>-0.02246113774208841</v>
       </c>
       <c r="Z7">
-        <v>0.3877250947084365</v>
+        <v>0.2950997869472586</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05735015747290043</v>
+        <v>0.09268934600768725</v>
       </c>
       <c r="AC7">
-        <v>-0.05735015747290043</v>
+        <v>-0.09268934600768725</v>
       </c>
       <c r="AD7">
-        <v>4741.2</v>
+        <v>7946.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4741.2</v>
+        <v>7946.3</v>
       </c>
       <c r="AG7">
-        <v>2515</v>
+        <v>5865.200000000001</v>
       </c>
       <c r="AH7">
-        <v>0.308428906915776</v>
+        <v>0.5119378946012112</v>
       </c>
       <c r="AI7">
-        <v>0.4246028192222958</v>
+        <v>0.5880311394615714</v>
       </c>
       <c r="AJ7">
-        <v>0.1913144022090538</v>
+        <v>0.4363695883460185</v>
       </c>
       <c r="AK7">
-        <v>0.2813199105145414</v>
+        <v>0.5130376214759935</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Banque Centrale Populaire (CBSE:BCP)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.033</v>
-      </c>
-      <c r="E8">
-        <v>-0.0551</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>220.6</v>
-      </c>
-      <c r="L8">
-        <v>0.1379612257661038</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>-0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>-0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1832.3</v>
-      </c>
-      <c r="V8">
-        <v>0.271576575908936</v>
-      </c>
-      <c r="W8">
-        <v>0.06220217115465952</v>
-      </c>
-      <c r="X8">
-        <v>0.07335379108672926</v>
-      </c>
-      <c r="Y8">
-        <v>-0.01115161993206974</v>
-      </c>
-      <c r="Z8">
-        <v>0.2336967641986496</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.05894539523120251</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05894539523120251</v>
-      </c>
-      <c r="AD8">
-        <v>5115.9</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>5115.9</v>
-      </c>
-      <c r="AG8">
-        <v>3283.599999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.4312556900563105</v>
-      </c>
-      <c r="AI8">
-        <v>0.4990440330101255</v>
-      </c>
-      <c r="AJ8">
-        <v>0.3273615472807935</v>
-      </c>
-      <c r="AK8">
-        <v>0.3900179354087729</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0306</v>
+        <v>0.04665</v>
       </c>
       <c r="E2">
-        <v>0.00437</v>
+        <v>0.04835</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>968.36</v>
+        <v>1490.5</v>
       </c>
       <c r="L2">
-        <v>0.1939318687040635</v>
+        <v>0.2307061263659722</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>177.8</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.008219646712372464</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1192888292519289</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>177.8</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.008219646712372464</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.1192888292519289</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>5653.5</v>
+        <v>4558.099999999999</v>
       </c>
       <c r="V2">
-        <v>0.3356507593478752</v>
+        <v>0.210719750729274</v>
       </c>
       <c r="W2">
-        <v>0.07480713784773631</v>
+        <v>0.1143212624276756</v>
       </c>
       <c r="X2">
-        <v>0.1617524565449917</v>
+        <v>0.1028604329773617</v>
       </c>
       <c r="Y2">
-        <v>-0.08694531869725534</v>
+        <v>0.01146082945031396</v>
       </c>
       <c r="Z2">
-        <v>0.1688595445563907</v>
+        <v>0.2035681617454065</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08488788474105519</v>
+        <v>0.07371512135377703</v>
       </c>
       <c r="AC2">
-        <v>-0.08488788474105519</v>
+        <v>-0.07371512135377703</v>
       </c>
       <c r="AD2">
-        <v>25437.5</v>
+        <v>24511.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>25437.5</v>
+        <v>24511.2</v>
       </c>
       <c r="AG2">
-        <v>19784</v>
+        <v>19953.1</v>
       </c>
       <c r="AH2">
-        <v>0.6016309965019667</v>
+        <v>0.5312088907575044</v>
       </c>
       <c r="AI2">
-        <v>0.6417598663878034</v>
+        <v>0.5920822835720307</v>
       </c>
       <c r="AJ2">
-        <v>0.5401420794268772</v>
+        <v>0.4798240677949799</v>
       </c>
       <c r="AK2">
-        <v>0.5821631610541556</v>
+        <v>0.5416121519427148</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Africa (CBSE:BOA)</t>
+          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00234</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E3">
-        <v>0.00437</v>
+        <v>0.0392</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>192</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.1744502998364529</v>
+        <v>0.223585548738923</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1579.8</v>
+        <v>260.9</v>
       </c>
       <c r="V3">
-        <v>0.4596584131048328</v>
+        <v>0.2399742457689477</v>
       </c>
       <c r="W3">
-        <v>0.07480713784773631</v>
+        <v>0.1241248817407758</v>
       </c>
       <c r="X3">
-        <v>0.1617524565449917</v>
+        <v>0.1497680901990648</v>
       </c>
       <c r="Y3">
-        <v>-0.08694531869725534</v>
+        <v>-0.02564320845828907</v>
       </c>
       <c r="Z3">
-        <v>0.1009817414441692</v>
+        <v>0.08687670259386474</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08481751050623643</v>
+        <v>0.07129544588530104</v>
       </c>
       <c r="AC3">
-        <v>-0.08481751050623643</v>
+        <v>-0.07129544588530104</v>
       </c>
       <c r="AD3">
-        <v>8517.200000000001</v>
+        <v>3856.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8517.200000000001</v>
+        <v>3856.9</v>
       </c>
       <c r="AG3">
-        <v>6937.400000000001</v>
+        <v>3596</v>
       </c>
       <c r="AH3">
-        <v>0.7124919483691788</v>
+        <v>0.7801015351631236</v>
       </c>
       <c r="AI3">
-        <v>0.7518382839740478</v>
+        <v>0.8445519838836822</v>
       </c>
       <c r="AJ3">
-        <v>0.6687101780361084</v>
+        <v>0.7678510420225487</v>
       </c>
       <c r="AK3">
-        <v>0.7116230882066327</v>
+        <v>0.8351331893448525</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -817,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
+          <t>Bank of Africa (CBSE:BOA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.103</v>
+        <v>0.0455</v>
       </c>
       <c r="E4">
-        <v>0.159</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>70.5</v>
+        <v>249.4</v>
       </c>
       <c r="L4">
-        <v>0.2534148094895758</v>
+        <v>0.1828847987093936</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -871,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>262.2</v>
+        <v>535.4</v>
       </c>
       <c r="V4">
-        <v>0.2952702702702703</v>
+        <v>0.1384822306140396</v>
       </c>
       <c r="W4">
-        <v>0.1249335459861776</v>
+        <v>0.1045176431145755</v>
       </c>
       <c r="X4">
-        <v>0.1948067725151487</v>
+        <v>0.1320591331965449</v>
       </c>
       <c r="Y4">
-        <v>-0.06987322652897114</v>
+        <v>-0.02754149008196946</v>
       </c>
       <c r="Z4">
-        <v>0.09208566416206018</v>
+        <v>0.1348449041342417</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08487825960676895</v>
+        <v>0.0712969061029646</v>
       </c>
       <c r="AC4">
-        <v>-0.08487825960676895</v>
+        <v>-0.0712969061029646</v>
       </c>
       <c r="AD4">
-        <v>3138.2</v>
+        <v>10619.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3138.2</v>
+        <v>10619.4</v>
       </c>
       <c r="AG4">
-        <v>2876</v>
+        <v>10084</v>
       </c>
       <c r="AH4">
-        <v>0.7794446376235656</v>
+        <v>0.7331004583862595</v>
       </c>
       <c r="AI4">
-        <v>0.8447375504710632</v>
+        <v>0.7672865999046256</v>
       </c>
       <c r="AJ4">
-        <v>0.7640807651434643</v>
+        <v>0.7228570199710398</v>
       </c>
       <c r="AK4">
-        <v>0.832947173308619</v>
+        <v>0.7579219529793759</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -936,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
+          <t>Crédit du Maroc S.A. (CBSE:CDM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0025</v>
+        <v>0.0365</v>
       </c>
       <c r="E5">
-        <v>-0.276</v>
+        <v>-0.00536</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -963,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>9.66</v>
+        <v>40.1</v>
       </c>
       <c r="L5">
-        <v>0.04216499345264077</v>
+        <v>0.1798206278026906</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -990,55 +993,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>113.9</v>
+        <v>175.2</v>
       </c>
       <c r="V5">
-        <v>0.252886323268206</v>
+        <v>0.199385455786958</v>
       </c>
       <c r="W5">
-        <v>0.01208104052026013</v>
+        <v>0.06901893287435457</v>
       </c>
       <c r="X5">
-        <v>0.2019786817067487</v>
+        <v>0.08200014169326551</v>
       </c>
       <c r="Y5">
-        <v>-0.1898976411864886</v>
+        <v>-0.01298120881891095</v>
       </c>
       <c r="Z5">
-        <v>0.1103867632249702</v>
+        <v>0.2514943047253863</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08488788474105519</v>
+        <v>0.07318781449040493</v>
       </c>
       <c r="AC5">
-        <v>-0.08488788474105519</v>
+        <v>-0.07318781449040493</v>
       </c>
       <c r="AD5">
-        <v>1694.9</v>
+        <v>424.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1694.9</v>
+        <v>424.4</v>
       </c>
       <c r="AG5">
-        <v>1581</v>
+        <v>249.2</v>
       </c>
       <c r="AH5">
-        <v>0.7900526732857875</v>
+        <v>0.3256849052259995</v>
       </c>
       <c r="AI5">
-        <v>0.7204675876726887</v>
+        <v>0.382963364013716</v>
       </c>
       <c r="AJ5">
-        <v>0.7782809884808506</v>
+        <v>0.2209415728344711</v>
       </c>
       <c r="AK5">
-        <v>0.7062449745376574</v>
+        <v>0.2670953912111468</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1055,7 +1058,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banque Centrale Populaire (CBSE:BCP)</t>
+          <t>Attijariwafa bank SA (CBSE:ATW)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1064,10 +1067,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0368</v>
+        <v>0.0478</v>
       </c>
       <c r="E6">
-        <v>-0.08019999999999999</v>
+        <v>0.0575</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1082,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>163</v>
+        <v>711.3</v>
       </c>
       <c r="L6">
-        <v>0.1208033795301267</v>
+        <v>0.2856741234587734</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1109,55 +1112,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1616.5</v>
+        <v>1954.5</v>
       </c>
       <c r="V6">
-        <v>0.3598299350013356</v>
+        <v>0.2076758789965255</v>
       </c>
       <c r="W6">
-        <v>0.04461597416105546</v>
+        <v>0.1457552099342226</v>
       </c>
       <c r="X6">
-        <v>0.1130275653939952</v>
+        <v>0.07959026078601485</v>
       </c>
       <c r="Y6">
-        <v>-0.06841159123293974</v>
+        <v>0.06616494914820779</v>
       </c>
       <c r="Z6">
-        <v>0.202127181484533</v>
+        <v>0.2530231896429079</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09215197647189804</v>
+        <v>0.07424242821714915</v>
       </c>
       <c r="AC6">
-        <v>-0.09215197647189804</v>
+        <v>-0.07424242821714915</v>
       </c>
       <c r="AD6">
-        <v>4140.9</v>
+        <v>3519.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4140.9</v>
+        <v>3519.9</v>
       </c>
       <c r="AG6">
-        <v>2524.4</v>
+        <v>1565.4</v>
       </c>
       <c r="AH6">
-        <v>0.4796427785435465</v>
+        <v>0.2722021158129176</v>
       </c>
       <c r="AI6">
-        <v>0.4744548964790264</v>
+        <v>0.3601068074396906</v>
       </c>
       <c r="AJ6">
-        <v>0.3597651351043211</v>
+        <v>0.1426111672907158</v>
       </c>
       <c r="AK6">
-        <v>0.354989312633592</v>
+        <v>0.200176468331607</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1174,7 +1177,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Attijariwafa bank SA (CBSE:ATW)</t>
+          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1183,10 +1186,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0306</v>
+        <v>0.0196</v>
       </c>
       <c r="E7">
-        <v>0.0191</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1201,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>533.2</v>
+        <v>33.8</v>
       </c>
       <c r="L7">
-        <v>0.2618731889396396</v>
+        <v>0.1251851851851852</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1228,60 +1231,182 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2081.1</v>
+        <v>141</v>
       </c>
       <c r="V7">
-        <v>0.2747072877753871</v>
+        <v>0.1940545004128819</v>
       </c>
       <c r="W7">
-        <v>0.09454738895292136</v>
+        <v>0.05155582672361195</v>
       </c>
       <c r="X7">
-        <v>0.1170085266950098</v>
+        <v>0.1163955593548316</v>
       </c>
       <c r="Y7">
-        <v>-0.02246113774208841</v>
+        <v>-0.0648397326312197</v>
       </c>
       <c r="Z7">
-        <v>0.2950997869472586</v>
+        <v>0.1211528365468749</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09268934600768725</v>
+        <v>0.07516785316858243</v>
       </c>
       <c r="AC7">
-        <v>-0.09268934600768725</v>
+        <v>-0.07516785316858243</v>
       </c>
       <c r="AD7">
-        <v>7946.3</v>
+        <v>1481.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>7946.3</v>
+        <v>1481.1</v>
       </c>
       <c r="AG7">
-        <v>5865.200000000001</v>
+        <v>1340.1</v>
       </c>
       <c r="AH7">
-        <v>0.5119378946012112</v>
+        <v>0.6708791955428727</v>
       </c>
       <c r="AI7">
-        <v>0.5880311394615714</v>
+        <v>0.6767339851960157</v>
       </c>
       <c r="AJ7">
-        <v>0.4363695883460185</v>
+        <v>0.6484250254028161</v>
       </c>
       <c r="AK7">
-        <v>0.5130376214759935</v>
+        <v>0.6544735299863255</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Banque Centrale Populaire (CBSE:BCP)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0576</v>
+      </c>
+      <c r="E8">
+        <v>0.0713</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>390.3</v>
+      </c>
+      <c r="L8">
+        <v>0.2143798747665605</v>
+      </c>
+      <c r="M8">
+        <v>177.8</v>
+      </c>
+      <c r="N8">
+        <v>0.03140732366501209</v>
+      </c>
+      <c r="O8">
+        <v>0.4555470151165769</v>
+      </c>
+      <c r="P8">
+        <v>177.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.03140732366501209</v>
+      </c>
+      <c r="R8">
+        <v>0.4555470151165769</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1491.1</v>
+      </c>
+      <c r="V8">
+        <v>0.2633940400275565</v>
+      </c>
+      <c r="W8">
+        <v>0.1304565813222809</v>
+      </c>
+      <c r="X8">
+        <v>0.08932530659989169</v>
+      </c>
+      <c r="Y8">
+        <v>0.0411312747223892</v>
+      </c>
+      <c r="Z8">
+        <v>0.3441197595735834</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07613868970938772</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07613868970938772</v>
+      </c>
+      <c r="AD8">
+        <v>4609.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>4609.5</v>
+      </c>
+      <c r="AG8">
+        <v>3118.4</v>
+      </c>
+      <c r="AH8">
+        <v>0.4488053278289486</v>
+      </c>
+      <c r="AI8">
+        <v>0.4646720229034567</v>
+      </c>
+      <c r="AJ8">
+        <v>0.3551910701064981</v>
+      </c>
+      <c r="AK8">
+        <v>0.3699696279422932</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04665</v>
+        <v>0.0534</v>
       </c>
       <c r="E2">
-        <v>0.04835</v>
+        <v>0.06415</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1490.5</v>
+        <v>1288.9</v>
       </c>
       <c r="L2">
-        <v>0.2307061263659722</v>
+        <v>0.2702833057227337</v>
       </c>
       <c r="M2">
-        <v>177.8</v>
+        <v>203.2</v>
       </c>
       <c r="N2">
-        <v>0.008219646712372464</v>
+        <v>0.01205898934749711</v>
       </c>
       <c r="O2">
-        <v>0.1192888292519289</v>
+        <v>0.1576538133291954</v>
       </c>
       <c r="P2">
-        <v>177.8</v>
+        <v>203.2</v>
       </c>
       <c r="Q2">
-        <v>0.008219646712372464</v>
+        <v>0.01205898934749711</v>
       </c>
       <c r="R2">
-        <v>0.1192888292519289</v>
+        <v>0.1576538133291954</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4558.099999999999</v>
+        <v>3633.1</v>
       </c>
       <c r="V2">
-        <v>0.210719750729274</v>
+        <v>0.2156078454645263</v>
       </c>
       <c r="W2">
-        <v>0.1143212624276756</v>
+        <v>0.1390995385445347</v>
       </c>
       <c r="X2">
-        <v>0.1028604329773617</v>
+        <v>0.08962941811216363</v>
       </c>
       <c r="Y2">
-        <v>0.01146082945031396</v>
+        <v>0.04947012043237103</v>
       </c>
       <c r="Z2">
-        <v>0.2035681617454065</v>
+        <v>0.388941903806471</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07371512135377703</v>
+        <v>0.07787017427175082</v>
       </c>
       <c r="AC2">
-        <v>-0.07371512135377703</v>
+        <v>-0.07787017427175082</v>
       </c>
       <c r="AD2">
-        <v>24511.2</v>
+        <v>9249.299999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24511.2</v>
+        <v>9249.299999999999</v>
       </c>
       <c r="AG2">
-        <v>19953.1</v>
+        <v>5616.199999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5312088907575044</v>
+        <v>0.3543820259159074</v>
       </c>
       <c r="AI2">
-        <v>0.5920822835720307</v>
+        <v>0.4205087404241776</v>
       </c>
       <c r="AJ2">
-        <v>0.4798240677949799</v>
+        <v>0.2499788575981341</v>
       </c>
       <c r="AK2">
-        <v>0.5416121519427148</v>
+        <v>0.3058532653683613</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
+          <t>Attijariwafa bank SA (CBSE:ATW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06900000000000001</v>
+        <v>0.0582</v>
       </c>
       <c r="E3">
-        <v>0.0392</v>
+        <v>0.08650000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>65.59999999999999</v>
+        <v>916.2</v>
       </c>
       <c r="L3">
-        <v>0.223585548738923</v>
+        <v>0.3106605181066052</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>260.9</v>
+        <v>2264.8</v>
       </c>
       <c r="V3">
-        <v>0.2399742457689477</v>
+        <v>0.1997653762359645</v>
       </c>
       <c r="W3">
-        <v>0.1241248817407758</v>
+        <v>0.1676548089591568</v>
       </c>
       <c r="X3">
-        <v>0.1497680901990648</v>
+        <v>0.08283740998527203</v>
       </c>
       <c r="Y3">
-        <v>-0.02564320845828907</v>
+        <v>0.08481739897388477</v>
       </c>
       <c r="Z3">
-        <v>0.08687670259386474</v>
+        <v>0.4965651939655171</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07129544588530104</v>
+        <v>0.07725017015008934</v>
       </c>
       <c r="AC3">
-        <v>-0.07129544588530104</v>
+        <v>-0.07725017015008934</v>
       </c>
       <c r="AD3">
-        <v>3856.9</v>
+        <v>3770</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3856.9</v>
+        <v>3770</v>
       </c>
       <c r="AG3">
-        <v>3596</v>
+        <v>1505.2</v>
       </c>
       <c r="AH3">
-        <v>0.7801015351631236</v>
+        <v>0.2495482316495999</v>
       </c>
       <c r="AI3">
-        <v>0.8445519838836822</v>
+        <v>0.3441979366383639</v>
       </c>
       <c r="AJ3">
-        <v>0.7678510420225487</v>
+        <v>0.1172045941210823</v>
       </c>
       <c r="AK3">
-        <v>0.8351331893448525</v>
+        <v>0.1732464722266983</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Africa (CBSE:BOA)</t>
+          <t>Banque Centrale Populaire (CBSE:BCP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0455</v>
+        <v>0.0486</v>
       </c>
       <c r="E4">
-        <v>0.06709999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,566 +847,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>249.4</v>
+        <v>372.7</v>
       </c>
       <c r="L4">
-        <v>0.1828847987093936</v>
+        <v>0.2048364935421819</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>203.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0368569977508525</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5452106251676951</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>203.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0368569977508525</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5452106251676951</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>535.4</v>
+        <v>1368.3</v>
       </c>
       <c r="V4">
-        <v>0.1384822306140396</v>
+        <v>0.2481861713705289</v>
       </c>
       <c r="W4">
-        <v>0.1045176431145755</v>
+        <v>0.1105442681299125</v>
       </c>
       <c r="X4">
-        <v>0.1320591331965449</v>
+        <v>0.09642142623905522</v>
       </c>
       <c r="Y4">
-        <v>-0.02754149008196946</v>
+        <v>0.01412284189085727</v>
       </c>
       <c r="Z4">
-        <v>0.1348449041342417</v>
+        <v>0.2878272561891956</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0712969061029646</v>
+        <v>0.0784901783934123</v>
       </c>
       <c r="AC4">
-        <v>-0.0712969061029646</v>
+        <v>-0.0784901783934123</v>
       </c>
       <c r="AD4">
-        <v>10619.4</v>
+        <v>5479.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10619.4</v>
+        <v>5479.3</v>
       </c>
       <c r="AG4">
-        <v>10084</v>
+        <v>4111</v>
       </c>
       <c r="AH4">
-        <v>0.7331004583862595</v>
+        <v>0.4984580395724358</v>
       </c>
       <c r="AI4">
-        <v>0.7672865999046256</v>
+        <v>0.4962010414308354</v>
       </c>
       <c r="AJ4">
-        <v>0.7228570199710398</v>
+        <v>0.4271523866918808</v>
       </c>
       <c r="AK4">
-        <v>0.7579219529793759</v>
+        <v>0.4249446982696243</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Crédit du Maroc S.A. (CBSE:CDM)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0365</v>
-      </c>
-      <c r="E5">
-        <v>-0.00536</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>40.1</v>
-      </c>
-      <c r="L5">
-        <v>0.1798206278026906</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>175.2</v>
-      </c>
-      <c r="V5">
-        <v>0.199385455786958</v>
-      </c>
-      <c r="W5">
-        <v>0.06901893287435457</v>
-      </c>
-      <c r="X5">
-        <v>0.08200014169326551</v>
-      </c>
-      <c r="Y5">
-        <v>-0.01298120881891095</v>
-      </c>
-      <c r="Z5">
-        <v>0.2514943047253863</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.07318781449040493</v>
-      </c>
-      <c r="AC5">
-        <v>-0.07318781449040493</v>
-      </c>
-      <c r="AD5">
-        <v>424.4</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>424.4</v>
-      </c>
-      <c r="AG5">
-        <v>249.2</v>
-      </c>
-      <c r="AH5">
-        <v>0.3256849052259995</v>
-      </c>
-      <c r="AI5">
-        <v>0.382963364013716</v>
-      </c>
-      <c r="AJ5">
-        <v>0.2209415728344711</v>
-      </c>
-      <c r="AK5">
-        <v>0.2670953912111468</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Attijariwafa bank SA (CBSE:ATW)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0478</v>
-      </c>
-      <c r="E6">
-        <v>0.0575</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>711.3</v>
-      </c>
-      <c r="L6">
-        <v>0.2856741234587734</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>-0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1954.5</v>
-      </c>
-      <c r="V6">
-        <v>0.2076758789965255</v>
-      </c>
-      <c r="W6">
-        <v>0.1457552099342226</v>
-      </c>
-      <c r="X6">
-        <v>0.07959026078601485</v>
-      </c>
-      <c r="Y6">
-        <v>0.06616494914820779</v>
-      </c>
-      <c r="Z6">
-        <v>0.2530231896429079</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.07424242821714915</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07424242821714915</v>
-      </c>
-      <c r="AD6">
-        <v>3519.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>3519.9</v>
-      </c>
-      <c r="AG6">
-        <v>1565.4</v>
-      </c>
-      <c r="AH6">
-        <v>0.2722021158129176</v>
-      </c>
-      <c r="AI6">
-        <v>0.3601068074396906</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1426111672907158</v>
-      </c>
-      <c r="AK6">
-        <v>0.200176468331607</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0196</v>
-      </c>
-      <c r="E7">
-        <v>-0.08800000000000001</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>33.8</v>
-      </c>
-      <c r="L7">
-        <v>0.1251851851851852</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>-0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>-0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>141</v>
-      </c>
-      <c r="V7">
-        <v>0.1940545004128819</v>
-      </c>
-      <c r="W7">
-        <v>0.05155582672361195</v>
-      </c>
-      <c r="X7">
-        <v>0.1163955593548316</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0648397326312197</v>
-      </c>
-      <c r="Z7">
-        <v>0.1211528365468749</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.07516785316858243</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07516785316858243</v>
-      </c>
-      <c r="AD7">
-        <v>1481.1</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>1481.1</v>
-      </c>
-      <c r="AG7">
-        <v>1340.1</v>
-      </c>
-      <c r="AH7">
-        <v>0.6708791955428727</v>
-      </c>
-      <c r="AI7">
-        <v>0.6767339851960157</v>
-      </c>
-      <c r="AJ7">
-        <v>0.6484250254028161</v>
-      </c>
-      <c r="AK7">
-        <v>0.6544735299863255</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Banque Centrale Populaire (CBSE:BCP)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0576</v>
-      </c>
-      <c r="E8">
-        <v>0.0713</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>390.3</v>
-      </c>
-      <c r="L8">
-        <v>0.2143798747665605</v>
-      </c>
-      <c r="M8">
-        <v>177.8</v>
-      </c>
-      <c r="N8">
-        <v>0.03140732366501209</v>
-      </c>
-      <c r="O8">
-        <v>0.4555470151165769</v>
-      </c>
-      <c r="P8">
-        <v>177.8</v>
-      </c>
-      <c r="Q8">
-        <v>0.03140732366501209</v>
-      </c>
-      <c r="R8">
-        <v>0.4555470151165769</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1491.1</v>
-      </c>
-      <c r="V8">
-        <v>0.2633940400275565</v>
-      </c>
-      <c r="W8">
-        <v>0.1304565813222809</v>
-      </c>
-      <c r="X8">
-        <v>0.08932530659989169</v>
-      </c>
-      <c r="Y8">
-        <v>0.0411312747223892</v>
-      </c>
-      <c r="Z8">
-        <v>0.3441197595735834</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.07613868970938772</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07613868970938772</v>
-      </c>
-      <c r="AD8">
-        <v>4609.5</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>4609.5</v>
-      </c>
-      <c r="AG8">
-        <v>3118.4</v>
-      </c>
-      <c r="AH8">
-        <v>0.4488053278289486</v>
-      </c>
-      <c r="AI8">
-        <v>0.4646720229034567</v>
-      </c>
-      <c r="AJ8">
-        <v>0.3551910701064981</v>
-      </c>
-      <c r="AK8">
-        <v>0.3699696279422932</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0534</v>
+        <v>0.0483</v>
       </c>
       <c r="E2">
         <v>0.06415</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1288.9</v>
+        <v>1804.5</v>
       </c>
       <c r="L2">
-        <v>0.2702833057227337</v>
+        <v>0.2484681583476764</v>
       </c>
       <c r="M2">
-        <v>203.2</v>
+        <v>290.599</v>
       </c>
       <c r="N2">
-        <v>0.01205898934749711</v>
+        <v>0.01200723080737129</v>
       </c>
       <c r="O2">
-        <v>0.1576538133291954</v>
+        <v>0.1610412856747021</v>
       </c>
       <c r="P2">
-        <v>203.2</v>
+        <v>290.599</v>
       </c>
       <c r="Q2">
-        <v>0.01205898934749711</v>
+        <v>0.01200723080737129</v>
       </c>
       <c r="R2">
-        <v>0.1576538133291954</v>
+        <v>0.1610412856747021</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3633.1</v>
+        <v>6249.5</v>
       </c>
       <c r="V2">
-        <v>0.2156078454645263</v>
+        <v>0.2582224609536402</v>
       </c>
       <c r="W2">
-        <v>0.1390995385445347</v>
+        <v>0.1202061914738003</v>
       </c>
       <c r="X2">
-        <v>0.08962941811216363</v>
+        <v>0.1090532110261563</v>
       </c>
       <c r="Y2">
-        <v>0.04947012043237103</v>
+        <v>0.01115298044764403</v>
       </c>
       <c r="Z2">
-        <v>0.388941903806471</v>
+        <v>0.2328301210524274</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07787017427175082</v>
+        <v>0.0765146696057485</v>
       </c>
       <c r="AC2">
-        <v>-0.07787017427175082</v>
+        <v>-0.0765146696057485</v>
       </c>
       <c r="AD2">
-        <v>9249.299999999999</v>
+        <v>25426.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9249.299999999999</v>
+        <v>25426.8</v>
       </c>
       <c r="AG2">
-        <v>5616.199999999999</v>
+        <v>19177.3</v>
       </c>
       <c r="AH2">
-        <v>0.3543820259159074</v>
+        <v>0.5123396092591398</v>
       </c>
       <c r="AI2">
-        <v>0.4205087404241776</v>
+        <v>0.5754062635072291</v>
       </c>
       <c r="AJ2">
-        <v>0.2499788575981341</v>
+        <v>0.4420841276830193</v>
       </c>
       <c r="AK2">
-        <v>0.3058532653683613</v>
+        <v>0.5054665549106743</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Attijariwafa bank SA (CBSE:ATW)</t>
+          <t>Crédit du Maroc S.A. (CBSE:CDM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0582</v>
+        <v>0.0385</v>
       </c>
       <c r="E3">
-        <v>0.08650000000000001</v>
+        <v>-0.00343</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>916.2</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.3106605181066052</v>
+        <v>0.231590181430096</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2264.8</v>
+        <v>167.2</v>
       </c>
       <c r="V3">
-        <v>0.1997653762359645</v>
+        <v>0.16743440817144</v>
       </c>
       <c r="W3">
-        <v>0.1676548089591568</v>
+        <v>0.09583394670984838</v>
       </c>
       <c r="X3">
-        <v>0.08283740998527203</v>
+        <v>0.0895556801014043</v>
       </c>
       <c r="Y3">
-        <v>0.08481739897388477</v>
+        <v>0.006278266608444077</v>
       </c>
       <c r="Z3">
-        <v>0.4965651939655171</v>
+        <v>0.3027463651050082</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07725017015008934</v>
+        <v>0.07628038877304213</v>
       </c>
       <c r="AC3">
-        <v>-0.07725017015008934</v>
+        <v>-0.07628038877304213</v>
       </c>
       <c r="AD3">
-        <v>3770</v>
+        <v>659</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3770</v>
+        <v>659</v>
       </c>
       <c r="AG3">
-        <v>1505.2</v>
+        <v>491.8</v>
       </c>
       <c r="AH3">
-        <v>0.2495482316495999</v>
+        <v>0.3975627413127413</v>
       </c>
       <c r="AI3">
-        <v>0.3441979366383639</v>
+        <v>0.4695738919766281</v>
       </c>
       <c r="AJ3">
-        <v>0.1172045941210823</v>
+        <v>0.3299785292538915</v>
       </c>
       <c r="AK3">
-        <v>0.1732464722266983</v>
+        <v>0.3978320660087364</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -820,117 +820,596 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Bank of Africa (CBSE:BOA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.048</v>
+      </c>
+      <c r="E4">
+        <v>0.118</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>341.6</v>
+      </c>
+      <c r="L4">
+        <v>0.2178849343028448</v>
+      </c>
+      <c r="M4">
+        <v>87.39900000000002</v>
+      </c>
+      <c r="N4">
+        <v>0.02002176303491249</v>
+      </c>
+      <c r="O4">
+        <v>0.2558518735362998</v>
+      </c>
+      <c r="P4">
+        <v>87.39900000000002</v>
+      </c>
+      <c r="Q4">
+        <v>0.02002176303491249</v>
+      </c>
+      <c r="R4">
+        <v>0.2558518735362998</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1760.4</v>
+      </c>
+      <c r="V4">
+        <v>0.4032804911573353</v>
+      </c>
+      <c r="W4">
+        <v>0.1325058184639255</v>
+      </c>
+      <c r="X4">
+        <v>0.1216926664927607</v>
+      </c>
+      <c r="Y4">
+        <v>0.01081315197116484</v>
+      </c>
+      <c r="Z4">
+        <v>0.133509324704079</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07648479357053403</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07648479357053403</v>
+      </c>
+      <c r="AD4">
+        <v>9711.299999999999</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>9711.299999999999</v>
+      </c>
+      <c r="AG4">
+        <v>7950.9</v>
+      </c>
+      <c r="AH4">
+        <v>0.6898945050261073</v>
+      </c>
+      <c r="AI4">
+        <v>0.7253517970780675</v>
+      </c>
+      <c r="AJ4">
+        <v>0.6455696202531646</v>
+      </c>
+      <c r="AK4">
+        <v>0.6837719298245614</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Banque Marocaine pour le Commerce et l'Industrie (CBSE:BCI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0288</v>
+      </c>
+      <c r="E5">
+        <v>-0.158</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>25.2</v>
+      </c>
+      <c r="L5">
+        <v>0.08232603724273113</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>196.7</v>
+      </c>
+      <c r="V5">
+        <v>0.2588157894736842</v>
+      </c>
+      <c r="W5">
+        <v>0.03574468085106383</v>
+      </c>
+      <c r="X5">
+        <v>0.1234119127752253</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08766723192416143</v>
+      </c>
+      <c r="Z5">
+        <v>0.1503017328154692</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07649028002059365</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07649028002059365</v>
+      </c>
+      <c r="AD5">
+        <v>1754.4</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1754.4</v>
+      </c>
+      <c r="AG5">
+        <v>1557.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.6977410117721922</v>
+      </c>
+      <c r="AI5">
+        <v>0.699382100857086</v>
+      </c>
+      <c r="AJ5">
+        <v>0.6720887086335592</v>
+      </c>
+      <c r="AK5">
+        <v>0.673803962280474</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Crédit Immobilier et Hôtelier, Société Anonyme (CBSE:CIH)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0897</v>
+      </c>
+      <c r="E6">
+        <v>0.186</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>83.7</v>
+      </c>
+      <c r="L6">
+        <v>0.2470484061393152</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>492.1</v>
+      </c>
+      <c r="V6">
+        <v>0.4008308218620184</v>
+      </c>
+      <c r="W6">
+        <v>0.1298681148176881</v>
+      </c>
+      <c r="X6">
+        <v>0.1437998517792601</v>
+      </c>
+      <c r="Y6">
+        <v>-0.01393173696157191</v>
+      </c>
+      <c r="Z6">
+        <v>0.08021782881496389</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07653905919090336</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07653905919090336</v>
+      </c>
+      <c r="AD6">
+        <v>4052.8</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>4052.8</v>
+      </c>
+      <c r="AG6">
+        <v>3560.7</v>
+      </c>
+      <c r="AH6">
+        <v>0.7675030773600985</v>
+      </c>
+      <c r="AI6">
+        <v>0.8282006743639522</v>
+      </c>
+      <c r="AJ6">
+        <v>0.7436095564280344</v>
+      </c>
+      <c r="AK6">
+        <v>0.808992593265779</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Attijariwafa bank SA (CBSE:ATW)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0582</v>
+      </c>
+      <c r="E7">
+        <v>0.08650000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>916.2</v>
+      </c>
+      <c r="L7">
+        <v>0.3106605181066052</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2264.8</v>
+      </c>
+      <c r="V7">
+        <v>0.1997653762359645</v>
+      </c>
+      <c r="W7">
+        <v>0.1676548089591568</v>
+      </c>
+      <c r="X7">
+        <v>0.08283179769571922</v>
+      </c>
+      <c r="Y7">
+        <v>0.08482301126343758</v>
+      </c>
+      <c r="Z7">
+        <v>0.4965651939655171</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.07724595839746994</v>
+      </c>
+      <c r="AC7">
+        <v>-0.07724595839746994</v>
+      </c>
+      <c r="AD7">
+        <v>3770</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>3770</v>
+      </c>
+      <c r="AG7">
+        <v>1505.2</v>
+      </c>
+      <c r="AH7">
+        <v>0.2495482316495999</v>
+      </c>
+      <c r="AI7">
+        <v>0.3441979366383639</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1172045941210823</v>
+      </c>
+      <c r="AK7">
+        <v>0.1732464722266983</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Banque Centrale Populaire (CBSE:BCP)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D8">
         <v>0.0486</v>
       </c>
-      <c r="E4">
+      <c r="E8">
         <v>0.0418</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>372.7</v>
       </c>
-      <c r="L4">
+      <c r="L8">
         <v>0.2048364935421819</v>
       </c>
-      <c r="M4">
+      <c r="M8">
         <v>203.2</v>
       </c>
-      <c r="N4">
+      <c r="N8">
         <v>0.0368569977508525</v>
       </c>
-      <c r="O4">
+      <c r="O8">
         <v>0.5452106251676951</v>
       </c>
-      <c r="P4">
+      <c r="P8">
         <v>203.2</v>
       </c>
-      <c r="Q4">
+      <c r="Q8">
         <v>0.0368569977508525</v>
       </c>
-      <c r="R4">
+      <c r="R8">
         <v>0.5452106251676951</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
         <v>1368.3</v>
       </c>
-      <c r="V4">
+      <c r="V8">
         <v>0.2481861713705289</v>
       </c>
-      <c r="W4">
+      <c r="W8">
         <v>0.1105442681299125</v>
       </c>
-      <c r="X4">
-        <v>0.09642142623905522</v>
-      </c>
-      <c r="Y4">
-        <v>0.01412284189085727</v>
-      </c>
-      <c r="Z4">
+      <c r="X8">
+        <v>0.09641375555955189</v>
+      </c>
+      <c r="Y8">
+        <v>0.0141305125703606</v>
+      </c>
+      <c r="Z8">
         <v>0.2878272561891956</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.0784901783934123</v>
-      </c>
-      <c r="AC4">
-        <v>-0.0784901783934123</v>
-      </c>
-      <c r="AD4">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.07848633122577639</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07848633122577639</v>
+      </c>
+      <c r="AD8">
         <v>5479.3</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>5479.3</v>
       </c>
-      <c r="AG4">
+      <c r="AG8">
         <v>4111</v>
       </c>
-      <c r="AH4">
+      <c r="AH8">
         <v>0.4984580395724358</v>
       </c>
-      <c r="AI4">
+      <c r="AI8">
         <v>0.4962010414308354</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ8">
         <v>0.4271523866918808</v>
       </c>
-      <c r="AK4">
+      <c r="AK8">
         <v>0.4249446982696243</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
